--- a/docs/RASRICH_Tagger_Sprint1_Sample Input to Tagger.xlsx
+++ b/docs/RASRICH_Tagger_Sprint1_Sample Input to Tagger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UN\fractals\VibeCoding\ClaudeCode\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B67BCEC-3BE3-4A37-AD41-A0363DF092C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA9473D-5473-44C4-865B-6AE7C0711403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{814581B4-0B3F-47C1-A026-55FC169981C5}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="604">
   <si>
     <t>Details</t>
   </si>
@@ -583,27 +583,6 @@
     <t>ATM CHECK DEPOSIT 09/09 204 W 4TH ST n</t>
   </si>
   <si>
-    <t>Automobile and truck expense</t>
-  </si>
-  <si>
-    <t>Fuel</t>
-  </si>
-  <si>
-    <t>Office expense</t>
-  </si>
-  <si>
-    <t>Legal and Professional</t>
-  </si>
-  <si>
-    <t>Repairs and maintenance</t>
-  </si>
-  <si>
-    <t>Postage/shipping</t>
-  </si>
-  <si>
-    <t>Permits and fees</t>
-  </si>
-  <si>
     <t>Online Transfer to  CHK ...9199 transaction#: 23146306732 12/30</t>
   </si>
   <si>
@@ -1876,94 +1855,7 @@
     <t>1/16/2024</t>
   </si>
   <si>
-    <t>Need Info</t>
-  </si>
-  <si>
-    <t>Credit Card</t>
-  </si>
-  <si>
-    <t>Auto Payment</t>
-  </si>
-  <si>
-    <t>Parking</t>
-  </si>
-  <si>
-    <t>Meals</t>
-  </si>
-  <si>
-    <t>Plumbing Services</t>
-  </si>
-  <si>
-    <t>Telephone</t>
-  </si>
-  <si>
-    <t>Auto Insurance</t>
-  </si>
-  <si>
-    <t>Cleaner</t>
-  </si>
-  <si>
-    <t>Exclude</t>
-  </si>
-  <si>
-    <t>Office Expense</t>
-  </si>
-  <si>
-    <t>tag from preparer</t>
-  </si>
-  <si>
-    <t>tag mapped to tax form</t>
-  </si>
-  <si>
-    <t>tag post preparer review</t>
-  </si>
-  <si>
-    <t>Insurance - Automobile and truck expense</t>
-  </si>
-  <si>
-    <t>Insurance - General</t>
-  </si>
-  <si>
-    <t>Insurance - Workers Compensation</t>
-  </si>
-  <si>
-    <t>Payroll Processing Expenses</t>
-  </si>
-  <si>
-    <t>Personal - ATM</t>
-  </si>
-  <si>
-    <t>Personal - Bank Charges</t>
-  </si>
-  <si>
-    <t>Personal - Contra</t>
-  </si>
-  <si>
-    <t>Personal - Not Deductible</t>
-  </si>
-  <si>
-    <t>Review with Client</t>
-  </si>
-  <si>
-    <t>Salaries and Wages to Non-Shareholders</t>
-  </si>
-  <si>
-    <t>Salaries and Wages to Shareholders</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Taxes and Licenses</t>
-  </si>
-  <si>
-    <t>Income / Not Tagged</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>tagger output</t>
+    <t>tag</t>
   </si>
 </sst>
 </file>
@@ -18345,7 +18237,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C306BD63-3133-4B86-B914-CFFBB717727B}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="1"/>
@@ -18357,265 +18249,74 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>621</v>
-      </c>
-      <c r="B1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="D1" t="s">
-        <v>623</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" t="s">
-        <v>185</v>
-      </c>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>630</v>
-      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D4" t="s">
-        <v>612</v>
-      </c>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" t="s">
-        <v>166</v>
-      </c>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>620</v>
-      </c>
+      <c r="B7" s="27"/>
+      <c r="D7" s="26"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>184</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" t="s">
-        <v>183</v>
-      </c>
-      <c r="D10" t="s">
-        <v>615</v>
-      </c>
+      <c r="A10" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
-        <v>624</v>
-      </c>
-      <c r="D12" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>627</v>
-      </c>
-      <c r="D15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>628</v>
-      </c>
-      <c r="D16" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>629</v>
-      </c>
-      <c r="D17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>636</v>
-      </c>
-      <c r="D24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D29" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D32" t="s">
-        <v>618</v>
-      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="25" t="s">
-        <v>619</v>
-      </c>
+      <c r="D33" s="25"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="25" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" t="s">
-        <v>139</v>
-      </c>
+      <c r="D35" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18670,10 +18371,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -18693,10 +18394,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="E3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -18716,10 +18417,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -18739,7 +18440,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="E5" t="s">
         <v>78</v>
@@ -18762,7 +18463,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="E6" t="s">
         <v>80</v>
@@ -18785,7 +18486,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E7" t="s">
         <v>81</v>
@@ -18808,10 +18509,10 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -18834,10 +18535,10 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -18857,7 +18558,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="E10" t="s">
         <v>82</v>
@@ -18883,10 +18584,10 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="E11" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -18906,10 +18607,10 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -18929,10 +18630,10 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -18952,13 +18653,13 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="E14" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F14" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H14">
         <v>-0.53266666666666673</v>
@@ -18975,10 +18676,10 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E15" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -19001,13 +18702,13 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H16">
         <v>-66.666666666666671</v>
@@ -19024,10 +18725,10 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -19047,10 +18748,10 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E18" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
@@ -19070,10 +18771,10 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="E19" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -19096,13 +18797,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="E20" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H20">
         <v>-12.8</v>
@@ -19119,10 +18820,10 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E21" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
@@ -19145,13 +18846,13 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E22" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F22" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H22">
         <v>-66.666666666666671</v>
@@ -19168,10 +18869,10 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E23" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -19191,13 +18892,13 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E24" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H24">
         <v>-86.666666666666671</v>
@@ -19214,13 +18915,13 @@
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E25" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F25" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H25">
         <v>-66.666666666666671</v>
@@ -19237,10 +18938,10 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E26" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -19260,10 +18961,10 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E27" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -19283,13 +18984,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E28" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F28" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H28">
         <v>-6.8520000000000003</v>
@@ -19309,10 +19010,10 @@
         <v>45638</v>
       </c>
       <c r="E29" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F29" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H29">
         <v>-26.666666666666668</v>
@@ -19332,7 +19033,7 @@
         <v>45638</v>
       </c>
       <c r="E30" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -19355,7 +19056,7 @@
         <v>45638</v>
       </c>
       <c r="E31" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F31" t="s">
         <v>8</v>
@@ -19378,7 +19079,7 @@
         <v>45608</v>
       </c>
       <c r="E32" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F32" t="s">
         <v>8</v>
@@ -19401,7 +19102,7 @@
         <v>45608</v>
       </c>
       <c r="E33" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F33" t="s">
         <v>8</v>
@@ -19424,7 +19125,7 @@
         <v>45608</v>
       </c>
       <c r="E34" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F34" t="s">
         <v>8</v>
@@ -19447,10 +19148,10 @@
         <v>45577</v>
       </c>
       <c r="E35" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F35" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H35">
         <v>-2</v>
@@ -19470,7 +19171,7 @@
         <v>45547</v>
       </c>
       <c r="E36" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -19493,10 +19194,10 @@
         <v>45547</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F37" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H37">
         <v>-0.19933333333333333</v>
@@ -19516,10 +19217,10 @@
         <v>45547</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H38">
         <v>-26.666666666666668</v>
@@ -19565,7 +19266,7 @@
         <v>45455</v>
       </c>
       <c r="E40" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -19588,7 +19289,7 @@
         <v>45455</v>
       </c>
       <c r="E41" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
@@ -19660,10 +19361,10 @@
         <v>45363</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F44" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H44">
         <v>-3673.4673333333335</v>
@@ -19683,7 +19384,7 @@
         <v>45334</v>
       </c>
       <c r="E45" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s">
         <v>8</v>
@@ -19706,7 +19407,7 @@
         <v>45334</v>
       </c>
       <c r="E46" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
@@ -19729,10 +19430,10 @@
         <v>45334</v>
       </c>
       <c r="E47" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F47" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H47">
         <v>-41.525999999999996</v>
@@ -19772,10 +19473,10 @@
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E49" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
@@ -19795,10 +19496,10 @@
         <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E50" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F50" t="s">
         <v>8</v>
@@ -19818,10 +19519,10 @@
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E51" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F51" t="s">
         <v>8</v>
@@ -19841,10 +19542,10 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="E52" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
@@ -19867,10 +19568,10 @@
         <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="E53" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F53" t="s">
         <v>8</v>
@@ -19890,10 +19591,10 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="E54" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
@@ -19916,10 +19617,10 @@
         <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="E55" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
@@ -19942,10 +19643,10 @@
         <v>7</v>
       </c>
       <c r="D56" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E56" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
@@ -19965,13 +19666,13 @@
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E57" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F57" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H57">
         <v>-66.666666666666671</v>
@@ -19988,10 +19689,10 @@
         <v>7</v>
       </c>
       <c r="D58" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E58" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
@@ -20011,7 +19712,7 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -20037,7 +19738,7 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -20063,13 +19764,13 @@
         <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E61" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F61" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H61">
         <v>-120.47</v>
@@ -20086,10 +19787,10 @@
         <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E62" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -20109,10 +19810,10 @@
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
@@ -20135,13 +19836,13 @@
         <v>7</v>
       </c>
       <c r="D64" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E64" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F64" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H64">
         <v>-43.627333333333333</v>
@@ -20158,10 +19859,10 @@
         <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F65" t="s">
         <v>8</v>
@@ -20181,10 +19882,10 @@
         <v>7</v>
       </c>
       <c r="D66" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E66" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F66" t="s">
         <v>8</v>
@@ -20204,13 +19905,13 @@
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E67" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F67" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H67">
         <v>-0.53266666666666673</v>
@@ -20227,13 +19928,13 @@
         <v>7</v>
       </c>
       <c r="D68" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F68" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H68">
         <v>-80</v>
@@ -20250,13 +19951,13 @@
         <v>7</v>
       </c>
       <c r="D69" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E69" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F69" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H69">
         <v>-66.666666666666671</v>
@@ -20273,13 +19974,13 @@
         <v>7</v>
       </c>
       <c r="D70" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F70" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H70">
         <v>-2.6839999999999997</v>
@@ -20296,7 +19997,7 @@
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E71" t="s">
         <v>18</v>
@@ -20319,10 +20020,10 @@
         <v>7</v>
       </c>
       <c r="D72" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E72" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F72" t="s">
         <v>8</v>
@@ -20342,7 +20043,7 @@
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
@@ -20368,10 +20069,10 @@
         <v>7</v>
       </c>
       <c r="D74" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E74" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -20391,13 +20092,13 @@
         <v>7</v>
       </c>
       <c r="D75" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E75" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F75" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H75">
         <v>-40</v>
@@ -20414,13 +20115,13 @@
         <v>7</v>
       </c>
       <c r="D76" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E76" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F76" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H76">
         <v>-1.6679999999999999</v>
@@ -20437,7 +20138,7 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E77" t="s">
         <v>16</v>
@@ -20463,13 +20164,13 @@
         <v>7</v>
       </c>
       <c r="D78" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E78" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F78" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H78">
         <v>-53.333333333333336</v>
@@ -20486,13 +20187,13 @@
         <v>7</v>
       </c>
       <c r="D79" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E79" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F79" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H79">
         <v>-743.81200000000001</v>
@@ -20509,10 +20210,10 @@
         <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E80" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -20532,10 +20233,10 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E81" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
@@ -20558,10 +20259,10 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E82" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
@@ -20584,10 +20285,10 @@
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E83" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
@@ -20610,10 +20311,10 @@
         <v>7</v>
       </c>
       <c r="D84" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E84" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
@@ -20633,10 +20334,10 @@
         <v>7</v>
       </c>
       <c r="D85" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E85" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="F85" t="s">
         <v>8</v>
@@ -20656,7 +20357,7 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E86" t="s">
         <v>16</v>
@@ -20682,7 +20383,7 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
@@ -20711,7 +20412,7 @@
         <v>45637</v>
       </c>
       <c r="E88" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F88" t="s">
         <v>8</v>
@@ -20734,7 +20435,7 @@
         <v>45637</v>
       </c>
       <c r="E89" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F89" t="s">
         <v>8</v>
@@ -20757,10 +20458,10 @@
         <v>45637</v>
       </c>
       <c r="E90" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F90" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H90">
         <v>-66.666666666666671</v>
@@ -20806,10 +20507,10 @@
         <v>45515</v>
       </c>
       <c r="E92" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F92" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H92">
         <v>-133.33333333333334</v>
@@ -20829,10 +20530,10 @@
         <v>45515</v>
       </c>
       <c r="E93" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F93" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H93">
         <v>-53.333333333333336</v>
@@ -20852,7 +20553,7 @@
         <v>45515</v>
       </c>
       <c r="E94" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -20875,10 +20576,10 @@
         <v>45515</v>
       </c>
       <c r="E95" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F95" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H95">
         <v>-0.19933333333333333</v>
@@ -20898,10 +20599,10 @@
         <v>45484</v>
       </c>
       <c r="E96" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F96" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H96">
         <v>-66.666666666666671</v>
@@ -20921,7 +20622,7 @@
         <v>45484</v>
       </c>
       <c r="E97" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F97" t="s">
         <v>8</v>
@@ -20944,7 +20645,7 @@
         <v>45484</v>
       </c>
       <c r="E98" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F98" t="s">
         <v>8</v>
@@ -20967,7 +20668,7 @@
         <v>45423</v>
       </c>
       <c r="E99" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="F99" t="s">
         <v>8</v>
@@ -21016,7 +20717,7 @@
         <v>45393</v>
       </c>
       <c r="E101" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F101" t="s">
         <v>8</v>
@@ -21039,7 +20740,7 @@
         <v>45393</v>
       </c>
       <c r="E102" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F102" t="s">
         <v>14</v>
@@ -21065,10 +20766,10 @@
         <v>45393</v>
       </c>
       <c r="E103" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F103" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H103">
         <v>-66.666666666666671</v>
@@ -21088,10 +20789,10 @@
         <v>45393</v>
       </c>
       <c r="E104" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F104" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H104">
         <v>-133.33333333333334</v>
@@ -21111,10 +20812,10 @@
         <v>45302</v>
       </c>
       <c r="E105" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F105" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H105">
         <v>-113.33333333333333</v>
@@ -21134,7 +20835,7 @@
         <v>45302</v>
       </c>
       <c r="E106" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F106" t="s">
         <v>9</v>
@@ -21157,10 +20858,10 @@
         <v>45302</v>
       </c>
       <c r="E107" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="F107" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H107">
         <v>-1.3986666666666667</v>
@@ -21226,13 +20927,13 @@
         <v>7</v>
       </c>
       <c r="D110" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E110" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F110" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H110">
         <v>-113.33333333333333</v>
@@ -21249,13 +20950,13 @@
         <v>7</v>
       </c>
       <c r="D111" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E111" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H111">
         <v>-80</v>
@@ -21272,7 +20973,7 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E112" t="s">
         <v>22</v>
@@ -21295,10 +20996,10 @@
         <v>7</v>
       </c>
       <c r="D113" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E113" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="F113" t="s">
         <v>8</v>
@@ -21318,10 +21019,10 @@
         <v>7</v>
       </c>
       <c r="D114" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E114" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
         <v>8</v>
@@ -21341,10 +21042,10 @@
         <v>7</v>
       </c>
       <c r="D115" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="E115" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
         <v>9</v>
@@ -21364,10 +21065,10 @@
         <v>7</v>
       </c>
       <c r="D116" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="E116" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F116" t="s">
         <v>8</v>
@@ -21387,10 +21088,10 @@
         <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E117" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F117" t="s">
         <v>14</v>
@@ -21413,10 +21114,10 @@
         <v>13</v>
       </c>
       <c r="D118" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E118" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F118" t="s">
         <v>14</v>
@@ -21439,10 +21140,10 @@
         <v>13</v>
       </c>
       <c r="D119" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E119" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F119" t="s">
         <v>14</v>
@@ -21465,10 +21166,10 @@
         <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E120" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F120" t="s">
         <v>14</v>
@@ -21491,13 +21192,13 @@
         <v>7</v>
       </c>
       <c r="D121" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E121" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F121" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H121">
         <v>-106.66666666666667</v>
@@ -21514,10 +21215,10 @@
         <v>7</v>
       </c>
       <c r="D122" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E122" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F122" t="s">
         <v>8</v>
@@ -21537,10 +21238,10 @@
         <v>7</v>
       </c>
       <c r="D123" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F123" t="s">
         <v>8</v>
@@ -21560,7 +21261,7 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
@@ -21586,13 +21287,13 @@
         <v>7</v>
       </c>
       <c r="D125" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E125" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F125" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H125">
         <v>-133.33333333333334</v>
@@ -21609,13 +21310,13 @@
         <v>7</v>
       </c>
       <c r="D126" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E126" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F126" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H126">
         <v>-41.525999999999996</v>
@@ -21632,13 +21333,13 @@
         <v>7</v>
       </c>
       <c r="D127" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E127" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="F127" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H127">
         <v>-43.627333333333333</v>
@@ -21655,13 +21356,13 @@
         <v>7</v>
       </c>
       <c r="D128" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E128" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F128" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H128">
         <v>-14.951333333333334</v>
@@ -21678,10 +21379,10 @@
         <v>7</v>
       </c>
       <c r="D129" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E129" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="F129" t="s">
         <v>8</v>
@@ -21701,7 +21402,7 @@
         <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E130" t="s">
         <v>24</v>
@@ -21727,10 +21428,10 @@
         <v>7</v>
       </c>
       <c r="D131" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E131" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F131" t="s">
         <v>9</v>
@@ -21750,13 +21451,13 @@
         <v>7</v>
       </c>
       <c r="D132" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E132" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="F132" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H132">
         <v>-40</v>
@@ -21773,10 +21474,10 @@
         <v>7</v>
       </c>
       <c r="D133" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E133" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F133" t="s">
         <v>9</v>
@@ -21796,13 +21497,13 @@
         <v>7</v>
       </c>
       <c r="D134" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E134" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F134" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H134">
         <v>-122.12466666666666</v>
@@ -21819,13 +21520,13 @@
         <v>7</v>
       </c>
       <c r="D135" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E135" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F135" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H135">
         <v>-23.333333333333332</v>
@@ -21842,13 +21543,13 @@
         <v>7</v>
       </c>
       <c r="D136" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E136" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F136" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H136">
         <v>-0.53266666666666673</v>
@@ -21865,7 +21566,7 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E137" t="s">
         <v>16</v>
@@ -21891,13 +21592,13 @@
         <v>7</v>
       </c>
       <c r="D138" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E138" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F138" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H138">
         <v>-133.33333333333334</v>
@@ -21914,10 +21615,10 @@
         <v>7</v>
       </c>
       <c r="D139" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E139" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F139" t="s">
         <v>8</v>
@@ -21937,10 +21638,10 @@
         <v>7</v>
       </c>
       <c r="D140" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E140" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F140" t="s">
         <v>8</v>
@@ -21960,13 +21661,13 @@
         <v>7</v>
       </c>
       <c r="D141" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E141" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F141" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H141">
         <v>-90.728666666666669</v>
@@ -21983,10 +21684,10 @@
         <v>7</v>
       </c>
       <c r="D142" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E142" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
@@ -22006,7 +21707,7 @@
         <v>10</v>
       </c>
       <c r="D143" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E143" t="s">
         <v>25</v>
@@ -22029,10 +21730,10 @@
         <v>7</v>
       </c>
       <c r="D144" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E144" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F144" t="s">
         <v>8</v>
@@ -22052,13 +21753,13 @@
         <v>7</v>
       </c>
       <c r="D145" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E145" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F145" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H145">
         <v>-26.666666666666668</v>
@@ -22075,10 +21776,10 @@
         <v>7</v>
       </c>
       <c r="D146" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E146" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F146" t="s">
         <v>8</v>
@@ -22098,13 +21799,13 @@
         <v>7</v>
       </c>
       <c r="D147" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E147" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F147" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H147">
         <v>-66.666666666666671</v>
@@ -22121,13 +21822,13 @@
         <v>7</v>
       </c>
       <c r="D148" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E148" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F148" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H148">
         <v>-30</v>
@@ -22144,13 +21845,13 @@
         <v>7</v>
       </c>
       <c r="D149" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E149" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F149" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H149">
         <v>-35</v>
@@ -22167,7 +21868,7 @@
         <v>10</v>
       </c>
       <c r="D150" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -22190,7 +21891,7 @@
         <v>10</v>
       </c>
       <c r="D151" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -22213,7 +21914,7 @@
         <v>10</v>
       </c>
       <c r="D152" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E152" t="s">
         <v>29</v>
@@ -22236,7 +21937,7 @@
         <v>10</v>
       </c>
       <c r="D153" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E153" t="s">
         <v>29</v>
@@ -22262,10 +21963,10 @@
         <v>45606</v>
       </c>
       <c r="E154" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F154" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H154">
         <v>-66.666666666666671</v>
@@ -22285,7 +21986,7 @@
         <v>45575</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F155" t="s">
         <v>14</v>
@@ -22311,10 +22012,10 @@
         <v>45575</v>
       </c>
       <c r="E156" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F156" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H156">
         <v>-66.666666666666671</v>
@@ -22334,7 +22035,7 @@
         <v>45575</v>
       </c>
       <c r="E157" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F157" t="s">
         <v>14</v>
@@ -22360,10 +22061,10 @@
         <v>45575</v>
       </c>
       <c r="E158" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F158" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H158">
         <v>-333.33333333333331</v>
@@ -22383,7 +22084,7 @@
         <v>45545</v>
       </c>
       <c r="E159" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F159" t="s">
         <v>14</v>
@@ -22409,10 +22110,10 @@
         <v>45545</v>
       </c>
       <c r="E160" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F160" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H160">
         <v>-190</v>
@@ -22432,10 +22133,10 @@
         <v>45545</v>
       </c>
       <c r="E161" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F161" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H161">
         <v>-0.19933333333333333</v>
@@ -22455,7 +22156,7 @@
         <v>45483</v>
       </c>
       <c r="E162" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="F162" t="s">
         <v>8</v>
@@ -22478,7 +22179,7 @@
         <v>45392</v>
       </c>
       <c r="E163" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F163" t="s">
         <v>9</v>
@@ -22501,10 +22202,10 @@
         <v>45392</v>
       </c>
       <c r="E164" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F164" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H164">
         <v>-50</v>
@@ -22524,10 +22225,10 @@
         <v>45392</v>
       </c>
       <c r="E165" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F165" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H165">
         <v>-66.666666666666671</v>
@@ -22547,10 +22248,10 @@
         <v>45361</v>
       </c>
       <c r="E166" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F166" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H166">
         <v>-66.666666666666671</v>
@@ -22570,10 +22271,10 @@
         <v>45361</v>
       </c>
       <c r="E167" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="F167" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H167">
         <v>-133.33333333333334</v>
@@ -22593,10 +22294,10 @@
         <v>45332</v>
       </c>
       <c r="E168" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F168" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H168">
         <v>-418.69333333333333</v>
@@ -22616,10 +22317,10 @@
         <v>45301</v>
       </c>
       <c r="E169" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="F169" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H169">
         <v>-12</v>
@@ -22636,13 +22337,13 @@
         <v>7</v>
       </c>
       <c r="D170" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E170" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F170" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H170">
         <v>-1</v>
@@ -22659,10 +22360,10 @@
         <v>13</v>
       </c>
       <c r="D171" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E171" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F171" t="s">
         <v>14</v>
@@ -22685,10 +22386,10 @@
         <v>13</v>
       </c>
       <c r="D172" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E172" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F172" t="s">
         <v>14</v>
@@ -22711,10 +22412,10 @@
         <v>13</v>
       </c>
       <c r="D173" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E173" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F173" t="s">
         <v>14</v>
@@ -22737,10 +22438,10 @@
         <v>7</v>
       </c>
       <c r="D174" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E174" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F174" t="s">
         <v>8</v>
@@ -22760,10 +22461,10 @@
         <v>7</v>
       </c>
       <c r="D175" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E175" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="F175" t="s">
         <v>9</v>
@@ -22783,13 +22484,13 @@
         <v>7</v>
       </c>
       <c r="D176" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E176" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F176" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H176">
         <v>-2.9333333333333331</v>
@@ -22806,13 +22507,13 @@
         <v>7</v>
       </c>
       <c r="D177" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E177" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="F177" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H177">
         <v>-41.360666666666667</v>
@@ -22829,7 +22530,7 @@
         <v>10</v>
       </c>
       <c r="D178" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E178" t="s">
         <v>30</v>
@@ -22852,10 +22553,10 @@
         <v>7</v>
       </c>
       <c r="D179" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E179" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F179" t="s">
         <v>8</v>
@@ -22875,13 +22576,13 @@
         <v>7</v>
       </c>
       <c r="D180" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E180" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F180" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H180">
         <v>-166.66666666666666</v>
@@ -22898,13 +22599,13 @@
         <v>7</v>
       </c>
       <c r="D181" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E181" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="F181" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H181">
         <v>-0.53266666666666673</v>
@@ -22921,7 +22622,7 @@
         <v>10</v>
       </c>
       <c r="D182" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E182" t="s">
         <v>31</v>
@@ -22944,7 +22645,7 @@
         <v>10</v>
       </c>
       <c r="D183" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E183" t="s">
         <v>32</v>
@@ -22967,10 +22668,10 @@
         <v>13</v>
       </c>
       <c r="D184" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E184" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F184" t="s">
         <v>14</v>
@@ -22993,10 +22694,10 @@
         <v>13</v>
       </c>
       <c r="D185" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E185" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F185" t="s">
         <v>14</v>
@@ -23019,7 +22720,7 @@
         <v>15</v>
       </c>
       <c r="D186" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="E186" t="s">
         <v>16</v>
@@ -23045,7 +22746,7 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
@@ -23071,13 +22772,13 @@
         <v>7</v>
       </c>
       <c r="D188" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="E188" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F188" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H188">
         <v>-2.2666666666666666</v>
@@ -23094,10 +22795,10 @@
         <v>7</v>
       </c>
       <c r="D189" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="E189" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F189" t="s">
         <v>8</v>
@@ -23117,10 +22818,10 @@
         <v>7</v>
       </c>
       <c r="D190" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="E190" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F190" t="s">
         <v>8</v>
@@ -23140,10 +22841,10 @@
         <v>13</v>
       </c>
       <c r="D191" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="E191" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F191" t="s">
         <v>14</v>
@@ -23166,7 +22867,7 @@
         <v>10</v>
       </c>
       <c r="D192" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="E192" t="s">
         <v>33</v>
@@ -23189,7 +22890,7 @@
         <v>13</v>
       </c>
       <c r="D193" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="E193" t="s">
         <v>34</v>
@@ -23215,10 +22916,10 @@
         <v>7</v>
       </c>
       <c r="D194" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E194" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F194" t="s">
         <v>8</v>
@@ -23238,10 +22939,10 @@
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E195" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F195" t="s">
         <v>14</v>
@@ -23264,10 +22965,10 @@
         <v>13</v>
       </c>
       <c r="D196" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E196" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F196" t="s">
         <v>14</v>
@@ -23290,13 +22991,13 @@
         <v>7</v>
       </c>
       <c r="D197" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E197" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="F197" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H197">
         <v>-53.333333333333336</v>
@@ -23313,13 +23014,13 @@
         <v>7</v>
       </c>
       <c r="D198" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E198" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F198" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H198">
         <v>-66.666666666666671</v>
@@ -23336,13 +23037,13 @@
         <v>7</v>
       </c>
       <c r="D199" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E199" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="F199" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H199">
         <v>-26.666666666666668</v>
@@ -23359,13 +23060,13 @@
         <v>7</v>
       </c>
       <c r="D200" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E200" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F200" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H200">
         <v>-66.666666666666671</v>
@@ -23385,10 +23086,10 @@
         <v>45635</v>
       </c>
       <c r="E201" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F201" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H201">
         <v>-66.666666666666671</v>
@@ -23408,10 +23109,10 @@
         <v>45605</v>
       </c>
       <c r="E202" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F202" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H202">
         <v>-66.666666666666671</v>
@@ -23431,10 +23132,10 @@
         <v>45605</v>
       </c>
       <c r="E203" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F203" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H203">
         <v>-66.666666666666671</v>
@@ -23454,7 +23155,7 @@
         <v>45605</v>
       </c>
       <c r="E204" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F204" t="s">
         <v>8</v>
@@ -23477,7 +23178,7 @@
         <v>45574</v>
       </c>
       <c r="E205" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="F205" t="s">
         <v>8</v>
@@ -23500,10 +23201,10 @@
         <v>45544</v>
       </c>
       <c r="E206" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F206" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H206">
         <v>-26.666666666666668</v>
@@ -23546,10 +23247,10 @@
         <v>45421</v>
       </c>
       <c r="E208" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F208" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H208">
         <v>-166.66666666666666</v>
@@ -23569,7 +23270,7 @@
         <v>45391</v>
       </c>
       <c r="E209" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="F209" t="s">
         <v>8</v>
@@ -23592,7 +23293,7 @@
         <v>45360</v>
       </c>
       <c r="E210" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="F210" t="s">
         <v>8</v>
@@ -23612,10 +23313,10 @@
         <v>13</v>
       </c>
       <c r="D211" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E211" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F211" t="s">
         <v>14</v>
@@ -23638,10 +23339,10 @@
         <v>13</v>
       </c>
       <c r="D212" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E212" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="F212" t="s">
         <v>14</v>
@@ -23664,10 +23365,10 @@
         <v>13</v>
       </c>
       <c r="D213" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E213" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F213" t="s">
         <v>14</v>
@@ -23690,10 +23391,10 @@
         <v>13</v>
       </c>
       <c r="D214" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E214" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F214" t="s">
         <v>14</v>
@@ -23716,10 +23417,10 @@
         <v>7</v>
       </c>
       <c r="D215" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E215" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="F215" t="s">
         <v>9</v>
@@ -23739,13 +23440,13 @@
         <v>7</v>
       </c>
       <c r="D216" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E216" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="F216" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H216">
         <v>-66.666666666666671</v>
@@ -23762,10 +23463,10 @@
         <v>7</v>
       </c>
       <c r="D217" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E217" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
         <v>9</v>
@@ -23785,10 +23486,10 @@
         <v>7</v>
       </c>
       <c r="D218" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E218" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="F218" t="s">
         <v>8</v>
@@ -23808,13 +23509,13 @@
         <v>7</v>
       </c>
       <c r="D219" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E219" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="F219" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H219">
         <v>-60</v>
@@ -23831,10 +23532,10 @@
         <v>7</v>
       </c>
       <c r="D220" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E220" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="F220" t="s">
         <v>9</v>
@@ -23854,7 +23555,7 @@
         <v>10</v>
       </c>
       <c r="D221" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E221" t="s">
         <v>36</v>
@@ -23877,7 +23578,7 @@
         <v>10</v>
       </c>
       <c r="D222" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E222" t="s">
         <v>37</v>
@@ -23900,13 +23601,13 @@
         <v>7</v>
       </c>
       <c r="D223" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="E223" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="F223" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H223">
         <v>-26.666666666666668</v>
@@ -23923,7 +23624,7 @@
         <v>13</v>
       </c>
       <c r="D224" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="E224" t="s">
         <v>38</v>
@@ -23949,10 +23650,10 @@
         <v>7</v>
       </c>
       <c r="D225" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E225" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F225" t="s">
         <v>8</v>
@@ -23972,13 +23673,13 @@
         <v>7</v>
       </c>
       <c r="D226" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E226" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F226" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H226">
         <v>-43.627333333333333</v>
@@ -23995,7 +23696,7 @@
         <v>10</v>
       </c>
       <c r="D227" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E227" t="s">
         <v>39</v>
@@ -24018,7 +23719,7 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E228" t="s">
         <v>16</v>
@@ -24044,10 +23745,10 @@
         <v>7</v>
       </c>
       <c r="D229" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E229" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="F229" t="s">
         <v>8</v>
@@ -24067,10 +23768,10 @@
         <v>7</v>
       </c>
       <c r="D230" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E230" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F230" t="s">
         <v>9</v>
@@ -24090,7 +23791,7 @@
         <v>10</v>
       </c>
       <c r="D231" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="E231" t="s">
         <v>40</v>
@@ -24113,7 +23814,7 @@
         <v>10</v>
       </c>
       <c r="D232" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E232" t="s">
         <v>41</v>
@@ -24139,10 +23840,10 @@
         <v>45634</v>
       </c>
       <c r="E233" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F233" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H233">
         <v>-26.666666666666668</v>
@@ -24162,7 +23863,7 @@
         <v>45634</v>
       </c>
       <c r="E234" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F234" t="s">
         <v>8</v>
@@ -24185,7 +23886,7 @@
         <v>45634</v>
       </c>
       <c r="E235" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="F235" t="s">
         <v>8</v>
@@ -24208,7 +23909,7 @@
         <v>45420</v>
       </c>
       <c r="E236" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F236" t="s">
         <v>8</v>
@@ -24231,10 +23932,10 @@
         <v>45420</v>
       </c>
       <c r="E237" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F237" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H237">
         <v>-26.666666666666668</v>
@@ -24254,7 +23955,7 @@
         <v>45420</v>
       </c>
       <c r="E238" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F238" t="s">
         <v>9</v>
@@ -24303,10 +24004,10 @@
         <v>45330</v>
       </c>
       <c r="E240" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F240" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H240">
         <v>-41.691333333333333</v>
@@ -24326,7 +24027,7 @@
         <v>45299</v>
       </c>
       <c r="E241" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="F241" t="s">
         <v>14</v>
@@ -24352,7 +24053,7 @@
         <v>45299</v>
       </c>
       <c r="E242" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="F242" t="s">
         <v>14</v>
@@ -24378,7 +24079,7 @@
         <v>45299</v>
       </c>
       <c r="E243" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="F243" t="s">
         <v>14</v>
@@ -24404,7 +24105,7 @@
         <v>45299</v>
       </c>
       <c r="E244" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="F244" t="s">
         <v>14</v>
@@ -24427,13 +24128,13 @@
         <v>7</v>
       </c>
       <c r="D245" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="E245" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="F245" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H245">
         <v>-33.333333333333336</v>
@@ -24450,10 +24151,10 @@
         <v>7</v>
       </c>
       <c r="D246" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E246" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F246" t="s">
         <v>8</v>
@@ -24473,10 +24174,10 @@
         <v>7</v>
       </c>
       <c r="D247" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E247" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="F247" t="s">
         <v>8</v>
@@ -24496,13 +24197,13 @@
         <v>7</v>
       </c>
       <c r="D248" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E248" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F248" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H248">
         <v>-66.666666666666671</v>
@@ -24519,7 +24220,7 @@
         <v>13</v>
       </c>
       <c r="D249" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="E249" t="s">
         <v>42</v>
@@ -24545,13 +24246,13 @@
         <v>7</v>
       </c>
       <c r="D250" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="E250" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F250" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H250">
         <v>-43.627333333333333</v>
@@ -24568,10 +24269,10 @@
         <v>7</v>
       </c>
       <c r="D251" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E251" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F251" t="s">
         <v>8</v>
@@ -24591,10 +24292,10 @@
         <v>7</v>
       </c>
       <c r="D252" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E252" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="F252" t="s">
         <v>8</v>
@@ -24614,7 +24315,7 @@
         <v>10</v>
       </c>
       <c r="D253" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E253" t="s">
         <v>43</v>
@@ -24637,10 +24338,10 @@
         <v>7</v>
       </c>
       <c r="D254" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E254" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F254" t="s">
         <v>8</v>
@@ -24715,7 +24416,7 @@
         <v>45511</v>
       </c>
       <c r="E257" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="F257" t="s">
         <v>14</v>
@@ -24741,7 +24442,7 @@
         <v>45511</v>
       </c>
       <c r="E258" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="F258" t="s">
         <v>14</v>
@@ -24767,7 +24468,7 @@
         <v>45511</v>
       </c>
       <c r="E259" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="F259" t="s">
         <v>14</v>
@@ -24793,7 +24494,7 @@
         <v>45511</v>
       </c>
       <c r="E260" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="F260" t="s">
         <v>14</v>
@@ -24819,7 +24520,7 @@
         <v>45511</v>
       </c>
       <c r="E261" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="F261" t="s">
         <v>8</v>
@@ -24842,7 +24543,7 @@
         <v>45419</v>
       </c>
       <c r="E262" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="F262" t="s">
         <v>8</v>
@@ -24865,7 +24566,7 @@
         <v>45419</v>
       </c>
       <c r="E263" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F263" t="s">
         <v>14</v>
@@ -24891,7 +24592,7 @@
         <v>45358</v>
       </c>
       <c r="E264" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F264" t="s">
         <v>8</v>
@@ -24937,7 +24638,7 @@
         <v>45298</v>
       </c>
       <c r="E266" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="F266" t="s">
         <v>8</v>
@@ -24957,13 +24658,13 @@
         <v>7</v>
       </c>
       <c r="D267" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="E267" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F267" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H267">
         <v>-1</v>
@@ -24980,10 +24681,10 @@
         <v>7</v>
       </c>
       <c r="D268" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E268" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F268" t="s">
         <v>8</v>
@@ -25003,7 +24704,7 @@
         <v>13</v>
       </c>
       <c r="D269" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E269" t="s">
         <v>45</v>
@@ -25029,13 +24730,13 @@
         <v>7</v>
       </c>
       <c r="D270" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="E270" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="F270" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H270">
         <v>-43.627333333333333</v>
@@ -25052,7 +24753,7 @@
         <v>10</v>
       </c>
       <c r="D271" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="E271" t="s">
         <v>46</v>
@@ -25075,7 +24776,7 @@
         <v>10</v>
       </c>
       <c r="D272" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="E272" t="s">
         <v>47</v>
@@ -25098,7 +24799,7 @@
         <v>10</v>
       </c>
       <c r="D273" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E273" t="s">
         <v>48</v>
@@ -25121,7 +24822,7 @@
         <v>10</v>
       </c>
       <c r="D274" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E274" t="s">
         <v>49</v>
@@ -25147,7 +24848,7 @@
         <v>45632</v>
       </c>
       <c r="E275" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="F275" t="s">
         <v>14</v>
@@ -25196,7 +24897,7 @@
         <v>45388</v>
       </c>
       <c r="E277" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F277" t="s">
         <v>8</v>
@@ -25216,10 +24917,10 @@
         <v>7</v>
       </c>
       <c r="D278" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="E278" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F278" t="s">
         <v>8</v>
@@ -25239,10 +24940,10 @@
         <v>13</v>
       </c>
       <c r="D279" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="E279" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F279" t="s">
         <v>14</v>
@@ -25265,10 +24966,10 @@
         <v>7</v>
       </c>
       <c r="D280" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="E280" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="F280" t="s">
         <v>8</v>
@@ -25288,7 +24989,7 @@
         <v>10</v>
       </c>
       <c r="D281" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="E281" t="s">
         <v>51</v>
@@ -25311,10 +25012,10 @@
         <v>7</v>
       </c>
       <c r="D282" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="E282" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="F282" t="s">
         <v>8</v>
@@ -25334,10 +25035,10 @@
         <v>13</v>
       </c>
       <c r="D283" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="E283" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="F283" t="s">
         <v>14</v>
@@ -25360,13 +25061,13 @@
         <v>7</v>
       </c>
       <c r="D284" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="E284" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F284" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H284">
         <v>-43.627333333333333</v>
@@ -25383,7 +25084,7 @@
         <v>13</v>
       </c>
       <c r="D285" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="E285" t="s">
         <v>52</v>
@@ -25409,10 +25110,10 @@
         <v>7</v>
       </c>
       <c r="D286" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E286" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F286" t="s">
         <v>8</v>
@@ -25432,10 +25133,10 @@
         <v>13</v>
       </c>
       <c r="D287" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E287" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="F287" t="s">
         <v>14</v>
@@ -25458,10 +25159,10 @@
         <v>13</v>
       </c>
       <c r="D288" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E288" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F288" t="s">
         <v>14</v>
@@ -25484,10 +25185,10 @@
         <v>13</v>
       </c>
       <c r="D289" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E289" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F289" t="s">
         <v>14</v>
@@ -25510,7 +25211,7 @@
         <v>15</v>
       </c>
       <c r="D290" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E290" t="s">
         <v>16</v>
@@ -25536,10 +25237,10 @@
         <v>13</v>
       </c>
       <c r="D291" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E291" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="F291" t="s">
         <v>14</v>
@@ -25562,10 +25263,10 @@
         <v>13</v>
       </c>
       <c r="D292" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E292" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F292" t="s">
         <v>14</v>
@@ -25588,10 +25289,10 @@
         <v>13</v>
       </c>
       <c r="D293" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="E293" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F293" t="s">
         <v>14</v>
@@ -25617,7 +25318,7 @@
         <v>45448</v>
       </c>
       <c r="E294" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="F294" t="s">
         <v>8</v>
@@ -25640,10 +25341,10 @@
         <v>45448</v>
       </c>
       <c r="E295" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F295" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H295">
         <v>-44</v>
@@ -25663,7 +25364,7 @@
         <v>45327</v>
       </c>
       <c r="E296" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F296" t="s">
         <v>14</v>
@@ -25689,7 +25390,7 @@
         <v>45327</v>
       </c>
       <c r="E297" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F297" t="s">
         <v>8</v>
@@ -25709,7 +25410,7 @@
         <v>15</v>
       </c>
       <c r="D298" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="E298" t="s">
         <v>16</v>
@@ -25735,10 +25436,10 @@
         <v>13</v>
       </c>
       <c r="D299" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E299" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F299" t="s">
         <v>14</v>
@@ -25761,10 +25462,10 @@
         <v>13</v>
       </c>
       <c r="D300" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E300" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="F300" t="s">
         <v>14</v>
@@ -25787,13 +25488,13 @@
         <v>7</v>
       </c>
       <c r="D301" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="E301" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F301" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H301">
         <v>-89.435999999999993</v>
@@ -25810,10 +25511,10 @@
         <v>13</v>
       </c>
       <c r="D302" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="E302" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F302" t="s">
         <v>14</v>
@@ -25836,7 +25537,7 @@
         <v>10</v>
       </c>
       <c r="D303" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="E303" t="s">
         <v>53</v>
@@ -25859,7 +25560,7 @@
         <v>13</v>
       </c>
       <c r="D304" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="E304" t="s">
         <v>54</v>
@@ -25885,13 +25586,13 @@
         <v>7</v>
       </c>
       <c r="D305" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="E305" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F305" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H305">
         <v>-45.333333333333336</v>
@@ -25911,7 +25612,7 @@
         <v>45600</v>
       </c>
       <c r="E306" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F306" t="s">
         <v>14</v>
@@ -25937,7 +25638,7 @@
         <v>45600</v>
       </c>
       <c r="E307" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F307" t="s">
         <v>14</v>
@@ -25963,7 +25664,7 @@
         <v>45600</v>
       </c>
       <c r="E308" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F308" t="s">
         <v>14</v>
@@ -25989,10 +25690,10 @@
         <v>45569</v>
       </c>
       <c r="E309" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F309" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H309">
         <v>-26.666666666666668</v>
@@ -26012,10 +25713,10 @@
         <v>45539</v>
       </c>
       <c r="E310" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="F310" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H310">
         <v>-36</v>
@@ -26035,10 +25736,10 @@
         <v>45539</v>
       </c>
       <c r="E311" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F311" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H311">
         <v>-100</v>
@@ -26058,7 +25759,7 @@
         <v>45508</v>
       </c>
       <c r="E312" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F312" t="s">
         <v>8</v>
@@ -26127,10 +25828,10 @@
         <v>45295</v>
       </c>
       <c r="E315" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F315" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H315">
         <v>-26.666666666666668</v>
@@ -26147,13 +25848,13 @@
         <v>7</v>
       </c>
       <c r="D316" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E316" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F316" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H316">
         <v>-1</v>
@@ -26170,10 +25871,10 @@
         <v>7</v>
       </c>
       <c r="D317" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E317" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F317" t="s">
         <v>9</v>
@@ -26193,13 +25894,13 @@
         <v>7</v>
       </c>
       <c r="D318" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E318" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F318" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H318">
         <v>-100</v>
@@ -26216,7 +25917,7 @@
         <v>15</v>
       </c>
       <c r="D319" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E319" t="s">
         <v>16</v>
@@ -26242,13 +25943,13 @@
         <v>7</v>
       </c>
       <c r="D320" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="E320" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F320" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H320">
         <v>-13.333333333333334</v>
@@ -26265,7 +25966,7 @@
         <v>10</v>
       </c>
       <c r="D321" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="E321" t="s">
         <v>58</v>
@@ -26288,10 +25989,10 @@
         <v>13</v>
       </c>
       <c r="D322" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="E322" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F322" t="s">
         <v>14</v>
@@ -26314,7 +26015,7 @@
         <v>15</v>
       </c>
       <c r="D323" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E323" t="s">
         <v>16</v>
@@ -26340,7 +26041,7 @@
         <v>15</v>
       </c>
       <c r="D324" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E324" t="s">
         <v>16</v>
@@ -26366,13 +26067,13 @@
         <v>7</v>
       </c>
       <c r="D325" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E325" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="F325" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H325">
         <v>-2.2666666666666666</v>
@@ -26389,13 +26090,13 @@
         <v>7</v>
       </c>
       <c r="D326" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E326" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="F326" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H326">
         <v>-2.2666666666666666</v>
@@ -26412,10 +26113,10 @@
         <v>7</v>
       </c>
       <c r="D327" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="E327" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F327" t="s">
         <v>8</v>
@@ -26435,10 +26136,10 @@
         <v>7</v>
       </c>
       <c r="D328" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="E328" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F328" t="s">
         <v>8</v>
@@ -26458,13 +26159,13 @@
         <v>7</v>
       </c>
       <c r="D329" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E329" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F329" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H329">
         <v>-2.2666666666666666</v>
@@ -26481,13 +26182,13 @@
         <v>7</v>
       </c>
       <c r="D330" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E330" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F330" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H330">
         <v>-2.2666666666666666</v>
@@ -26504,10 +26205,10 @@
         <v>13</v>
       </c>
       <c r="D331" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="E331" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F331" t="s">
         <v>14</v>
@@ -26530,10 +26231,10 @@
         <v>13</v>
       </c>
       <c r="D332" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="E332" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="F332" t="s">
         <v>14</v>
@@ -26651,10 +26352,10 @@
         <v>45446</v>
       </c>
       <c r="E337" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F337" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H337">
         <v>-2.2666666666666666</v>
@@ -26674,10 +26375,10 @@
         <v>45415</v>
       </c>
       <c r="E338" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="F338" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H338">
         <v>-2.2666666666666666</v>
@@ -26697,10 +26398,10 @@
         <v>45415</v>
       </c>
       <c r="E339" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="F339" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H339">
         <v>-2</v>
@@ -26720,7 +26421,7 @@
         <v>45415</v>
       </c>
       <c r="E340" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="F340" t="s">
         <v>8</v>
@@ -26766,7 +26467,7 @@
         <v>45385</v>
       </c>
       <c r="E342" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="F342" t="s">
         <v>8</v>
@@ -26812,10 +26513,10 @@
         <v>45294</v>
       </c>
       <c r="E344" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F344" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H344">
         <v>-2.2666666666666666</v>
@@ -26832,10 +26533,10 @@
         <v>13</v>
       </c>
       <c r="D345" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E345" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="F345" t="s">
         <v>14</v>
@@ -26858,10 +26559,10 @@
         <v>13</v>
       </c>
       <c r="D346" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E346" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F346" t="s">
         <v>14</v>
@@ -26884,10 +26585,10 @@
         <v>13</v>
       </c>
       <c r="D347" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E347" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="F347" t="s">
         <v>14</v>
@@ -26910,13 +26611,13 @@
         <v>7</v>
       </c>
       <c r="D348" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E348" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F348" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H348">
         <v>-133.33333333333334</v>
@@ -26933,10 +26634,10 @@
         <v>13</v>
       </c>
       <c r="D349" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E349" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="F349" t="s">
         <v>14</v>
@@ -26959,7 +26660,7 @@
         <v>10</v>
       </c>
       <c r="D350" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E350" t="s">
         <v>62</v>
@@ -26982,10 +26683,10 @@
         <v>7</v>
       </c>
       <c r="D351" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="E351" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="F351" t="s">
         <v>8</v>
@@ -27005,10 +26706,10 @@
         <v>7</v>
       </c>
       <c r="D352" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="E352" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="F352" t="s">
         <v>8</v>
@@ -27028,13 +26729,13 @@
         <v>7</v>
       </c>
       <c r="D353" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="E353" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="F353" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H353">
         <v>-16</v>
@@ -27051,13 +26752,13 @@
         <v>7</v>
       </c>
       <c r="D354" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="E354" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F354" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H354">
         <v>-43.627333333333333</v>
@@ -27074,7 +26775,7 @@
         <v>10</v>
       </c>
       <c r="D355" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="E355" t="s">
         <v>63</v>
@@ -27097,13 +26798,13 @@
         <v>7</v>
       </c>
       <c r="D356" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E356" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F356" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H356">
         <v>-1.6666666666666667</v>
@@ -27120,13 +26821,13 @@
         <v>7</v>
       </c>
       <c r="D357" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E357" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="F357" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H357">
         <v>-10.666666666666666</v>
@@ -27143,13 +26844,13 @@
         <v>7</v>
       </c>
       <c r="D358" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E358" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="F358" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="H358">
         <v>-272.57266666666669</v>
@@ -27166,7 +26867,7 @@
         <v>10</v>
       </c>
       <c r="D359" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E359" t="s">
         <v>64</v>
@@ -27189,13 +26890,13 @@
         <v>7</v>
       </c>
       <c r="D360" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E360" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="F360" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H360">
         <v>-2</v>
@@ -27212,10 +26913,10 @@
         <v>13</v>
       </c>
       <c r="D361" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E361" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F361" t="s">
         <v>14</v>
@@ -27238,10 +26939,10 @@
         <v>13</v>
       </c>
       <c r="D362" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E362" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="F362" t="s">
         <v>14</v>
@@ -27264,10 +26965,10 @@
         <v>7</v>
       </c>
       <c r="D363" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="E363" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="F363" t="s">
         <v>8</v>
@@ -27313,10 +27014,10 @@
         <v>45475</v>
       </c>
       <c r="E365" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F365" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H365">
         <v>-0.59866666666666668</v>
@@ -27336,10 +27037,10 @@
         <v>45414</v>
       </c>
       <c r="E366" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F366" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H366">
         <v>-0.59866666666666668</v>
@@ -27359,10 +27060,10 @@
         <v>45293</v>
       </c>
       <c r="E367" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="F367" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H367">
         <v>-23.4</v>
@@ -27402,13 +27103,13 @@
         <v>7</v>
       </c>
       <c r="D369" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="E369" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F369" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H369">
         <v>-1</v>
@@ -27425,7 +27126,7 @@
         <v>10</v>
       </c>
       <c r="D370" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E370" t="s">
         <v>67</v>
@@ -27448,10 +27149,10 @@
         <v>7</v>
       </c>
       <c r="D371" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E371" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F371" t="s">
         <v>8</v>
@@ -27471,10 +27172,10 @@
         <v>7</v>
       </c>
       <c r="D372" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E372" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="F372" t="s">
         <v>8</v>
@@ -27494,7 +27195,7 @@
         <v>10</v>
       </c>
       <c r="D373" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E373" t="s">
         <v>68</v>
@@ -27517,7 +27218,7 @@
         <v>10</v>
       </c>
       <c r="D374" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E374" t="s">
         <v>69</v>
@@ -27540,10 +27241,10 @@
         <v>13</v>
       </c>
       <c r="D375" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E375" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F375" t="s">
         <v>14</v>
@@ -27566,10 +27267,10 @@
         <v>13</v>
       </c>
       <c r="D376" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E376" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="F376" t="s">
         <v>14</v>
@@ -27592,10 +27293,10 @@
         <v>7</v>
       </c>
       <c r="D377" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E377" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="F377" t="s">
         <v>8</v>
@@ -27615,13 +27316,13 @@
         <v>7</v>
       </c>
       <c r="D378" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E378" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="F378" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H378">
         <v>-43.627333333333333</v>
@@ -27638,7 +27339,7 @@
         <v>10</v>
       </c>
       <c r="D379" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="E379" t="s">
         <v>59</v>
@@ -27661,7 +27362,7 @@
         <v>10</v>
       </c>
       <c r="D380" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="E380" t="s">
         <v>59</v>
@@ -27684,7 +27385,7 @@
         <v>10</v>
       </c>
       <c r="D381" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="E381" t="s">
         <v>59</v>
@@ -27707,13 +27408,13 @@
         <v>7</v>
       </c>
       <c r="D382" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="E382" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F382" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H382">
         <v>-2.2666666666666666</v>
@@ -27730,13 +27431,13 @@
         <v>7</v>
       </c>
       <c r="D383" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="E383" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="F383" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H383">
         <v>-2.2666666666666666</v>
@@ -27753,10 +27454,10 @@
         <v>7</v>
       </c>
       <c r="D384" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="E384" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F384" t="s">
         <v>8</v>
@@ -27776,10 +27477,10 @@
         <v>13</v>
       </c>
       <c r="D385" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="E385" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="F385" t="s">
         <v>14</v>
@@ -27802,13 +27503,13 @@
         <v>7</v>
       </c>
       <c r="D386" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E386" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F386" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H386">
         <v>-2.2666666666666666</v>
@@ -27825,13 +27526,13 @@
         <v>7</v>
       </c>
       <c r="D387" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E387" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="F387" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H387">
         <v>-2.2666666666666666</v>
@@ -27848,10 +27549,10 @@
         <v>7</v>
       </c>
       <c r="D388" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E388" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="F388" t="s">
         <v>8</v>
@@ -27871,10 +27572,10 @@
         <v>7</v>
       </c>
       <c r="D389" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E389" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F389" t="s">
         <v>8</v>
@@ -27894,7 +27595,7 @@
         <v>15</v>
       </c>
       <c r="D390" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E390" t="s">
         <v>16</v>
@@ -27920,7 +27621,7 @@
         <v>15</v>
       </c>
       <c r="D391" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E391" t="s">
         <v>16</v>
@@ -27946,7 +27647,7 @@
         <v>15</v>
       </c>
       <c r="D392" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E392" t="s">
         <v>16</v>
@@ -27975,7 +27676,7 @@
         <v>45566</v>
       </c>
       <c r="E393" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="F393" t="s">
         <v>14</v>
@@ -28001,7 +27702,7 @@
         <v>45566</v>
       </c>
       <c r="E394" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F394" t="s">
         <v>14</v>
@@ -28027,10 +27728,10 @@
         <v>45566</v>
       </c>
       <c r="E395" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="F395" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H395">
         <v>-23.4</v>
@@ -28073,10 +27774,10 @@
         <v>45536</v>
       </c>
       <c r="E397" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F397" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H397">
         <v>-1.3333333333333333</v>
@@ -28096,10 +27797,10 @@
         <v>45505</v>
       </c>
       <c r="E398" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F398" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H398">
         <v>-2.6666666666666665</v>
@@ -28119,7 +27820,7 @@
         <v>45413</v>
       </c>
       <c r="E399" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F399" t="s">
         <v>8</v>
@@ -28142,7 +27843,7 @@
         <v>45352</v>
       </c>
       <c r="E400" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F400" t="s">
         <v>8</v>
